--- a/EmployeeTemplateInterfaces_LAST/Employees.xlsx
+++ b/EmployeeTemplateInterfaces_LAST/Employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Visual Studio 2015\Projects\NodalPay - 2019\EmployeeTemplateInterfaces_LAST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93EF100C-D61F-459C-BF2B-321F797E71B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC6CE34-885A-4BEC-8172-3ADC949AF68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>Employment Status</t>
   </si>
@@ -52,9 +52,6 @@
     <t>Pay rate</t>
   </si>
   <si>
-    <t>Annual Leave Available Balance</t>
-  </si>
-  <si>
     <t>Address Line 1</t>
   </si>
   <si>
@@ -97,12 +94,6 @@
     <t>Nationality</t>
   </si>
   <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
     <t>Job Title</t>
   </si>
   <si>
@@ -127,9 +118,6 @@
     <t>Working Hours</t>
   </si>
   <si>
-    <t>DESK</t>
-  </si>
-  <si>
     <t>Cypriot</t>
   </si>
   <si>
@@ -151,9 +139,6 @@
     <t>Revolut</t>
   </si>
   <si>
-    <t>analysis</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Street</t>
   </si>
   <si>
@@ -176,6 +161,21 @@
   </si>
   <si>
     <t>PIRBCY2NXXX</t>
+  </si>
+  <si>
+    <t>Analysis 2</t>
+  </si>
+  <si>
+    <t>Analysis 3</t>
+  </si>
+  <si>
+    <t>Analysis 4</t>
+  </si>
+  <si>
+    <t>Analysis 1</t>
+  </si>
+  <si>
+    <t>Empty</t>
   </si>
 </sst>
 </file>
@@ -603,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
@@ -641,9 +641,11 @@
     <col min="34" max="34" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -672,88 +674,94 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="AI1" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>34</v>
+        <v>47</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -790,23 +798,25 @@
       <c r="AH2" s="3"/>
       <c r="AI2" s="3"/>
       <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B3" s="8">
         <v>10001</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G3" s="9">
         <v>33925</v>
@@ -819,26 +829,26 @@
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L3" s="6"/>
       <c r="M3" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O3" s="6">
         <v>99999999</v>
       </c>
       <c r="P3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R3" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="Q3" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="S3" s="6">
         <v>1111111</v>
@@ -848,24 +858,24 @@
       <c r="V3" s="6"/>
       <c r="W3" s="6"/>
       <c r="X3" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Y3" s="6"/>
       <c r="Z3" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB3" s="6"/>
       <c r="AC3" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="AD3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE3" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="AE3" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="AF3" s="7"/>
       <c r="AG3" s="6"/>
@@ -874,6 +884,8 @@
       </c>
       <c r="AI3" s="6"/>
       <c r="AJ3" s="6"/>
+      <c r="AK3" s="6"/>
+      <c r="AL3" s="6"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
